--- a/data/processed/puma_token_counts.xlsx
+++ b/data/processed/puma_token_counts.xlsx
@@ -434,12 +434,12 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Leadership_context_human</t>
+          <t>Leadership_context</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Information_valence_human</t>
+          <t>Information_valence</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
